--- a/R_analysis/output/tables/Tabela_Desigualdades_Raciais.xlsx
+++ b/R_analysis/output/tables/Tabela_Desigualdades_Raciais.xlsx
@@ -367,62 +367,62 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>n_casos_Branca</t>
+          <t>n_casos_Black</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>n_casos_Parda</t>
+          <t>n_casos_Mixed-race</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>n_casos_Preta</t>
+          <t>n_casos_White</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>taxa_1000nv_Branca</t>
+          <t>taxa_1000nv_Black</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>taxa_1000nv_Parda</t>
+          <t>taxa_1000nv_Mixed-race</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>taxa_1000nv_Preta</t>
+          <t>taxa_1000nv_White</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>diff_abs_preta</t>
+          <t>diff_abs_black</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>diff_abs_parda</t>
+          <t>diff_abs_mixed</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>razao_preta_branca</t>
+          <t>ratio_black_white</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>razao_parda_branca</t>
+          <t>ratio_mixed_white</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>diff_taxa_preta</t>
+          <t>diff_rate_black</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>diff_taxa_parda</t>
+          <t>diff_rate_mixed</t>
         </is>
       </c>
     </row>
@@ -432,17 +432,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C2">
-        <v>1695</v>
+        <v>657</v>
       </c>
       <c r="D2">
         <v>2571</v>
       </c>
       <c r="E2">
-        <v>657</v>
+        <v>1695</v>
       </c>
       <c r="I2">
         <v>-1038</v>
@@ -457,17 +457,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C3">
-        <v>2166</v>
+        <v>829</v>
       </c>
       <c r="D3">
         <v>3277</v>
       </c>
       <c r="E3">
-        <v>829</v>
+        <v>2166</v>
       </c>
       <c r="I3">
         <v>-1337</v>
@@ -482,17 +482,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C4">
-        <v>2402</v>
+        <v>1043</v>
       </c>
       <c r="D4">
         <v>3735</v>
       </c>
       <c r="E4">
-        <v>1043</v>
+        <v>2402</v>
       </c>
       <c r="I4">
         <v>-1359</v>
@@ -507,17 +507,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C5">
-        <v>2883</v>
+        <v>1180</v>
       </c>
       <c r="D5">
         <v>4522</v>
       </c>
       <c r="E5">
-        <v>1180</v>
+        <v>2883</v>
       </c>
       <c r="I5">
         <v>-1703</v>
@@ -532,17 +532,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C6">
-        <v>3848</v>
+        <v>1763</v>
       </c>
       <c r="D6">
         <v>6265</v>
       </c>
       <c r="E6">
-        <v>1763</v>
+        <v>3848</v>
       </c>
       <c r="I6">
         <v>-2085</v>
@@ -557,17 +557,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C7">
-        <v>4650</v>
+        <v>2034</v>
       </c>
       <c r="D7">
         <v>7492</v>
       </c>
       <c r="E7">
-        <v>2034</v>
+        <v>4650</v>
       </c>
       <c r="I7">
         <v>-2616</v>
@@ -582,17 +582,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C8">
-        <v>6118</v>
+        <v>2474</v>
       </c>
       <c r="D8">
         <v>9479</v>
       </c>
       <c r="E8">
-        <v>2474</v>
+        <v>6118</v>
       </c>
       <c r="I8">
         <v>-3644</v>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C9">
-        <v>7867</v>
+        <v>3270</v>
       </c>
       <c r="D9">
         <v>12346</v>
       </c>
       <c r="E9">
-        <v>3270</v>
+        <v>7867</v>
       </c>
       <c r="I9">
         <v>-4597</v>
@@ -632,17 +632,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C10">
-        <v>9904</v>
+        <v>3950</v>
       </c>
       <c r="D10">
         <v>15032</v>
       </c>
       <c r="E10">
-        <v>3950</v>
+        <v>9904</v>
       </c>
       <c r="I10">
         <v>-5954</v>
@@ -657,17 +657,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C11">
-        <v>11734</v>
+        <v>4734</v>
       </c>
       <c r="D11">
         <v>17861</v>
       </c>
       <c r="E11">
-        <v>4734</v>
+        <v>11734</v>
       </c>
       <c r="I11">
         <v>-7000</v>
@@ -682,17 +682,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C12">
-        <v>15100</v>
+        <v>6248</v>
       </c>
       <c r="D12">
         <v>23706</v>
       </c>
       <c r="E12">
-        <v>6248</v>
+        <v>15100</v>
       </c>
       <c r="I12">
         <v>-8852</v>
@@ -707,17 +707,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C13">
-        <v>18156</v>
+        <v>7720</v>
       </c>
       <c r="D13">
         <v>31977</v>
       </c>
       <c r="E13">
-        <v>7720</v>
+        <v>18156</v>
       </c>
       <c r="I13">
         <v>-10436</v>
@@ -732,17 +732,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C14">
-        <v>18444</v>
+        <v>7869</v>
       </c>
       <c r="D14">
         <v>33279</v>
       </c>
       <c r="E14">
-        <v>7869</v>
+        <v>18444</v>
       </c>
       <c r="I14">
         <v>-10575</v>
@@ -757,17 +757,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C15">
-        <v>17936</v>
+        <v>8022</v>
       </c>
       <c r="D15">
         <v>34277</v>
       </c>
       <c r="E15">
-        <v>8022</v>
+        <v>17936</v>
       </c>
       <c r="I15">
         <v>-9914</v>
@@ -782,17 +782,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C16">
-        <v>20413</v>
+        <v>8987</v>
       </c>
       <c r="D16">
         <v>40032</v>
       </c>
       <c r="E16">
-        <v>8987</v>
+        <v>20413</v>
       </c>
       <c r="I16">
         <v>-11426</v>
@@ -807,17 +807,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C17">
-        <v>23973</v>
+        <v>9767</v>
       </c>
       <c r="D17">
         <v>43515</v>
       </c>
       <c r="E17">
-        <v>9767</v>
+        <v>23973</v>
       </c>
       <c r="I17">
         <v>-14206</v>
@@ -832,17 +832,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C18">
-        <v>25244</v>
+        <v>10947</v>
       </c>
       <c r="D18">
         <v>46117</v>
       </c>
       <c r="E18">
-        <v>10947</v>
+        <v>25244</v>
       </c>
       <c r="I18">
         <v>-14297</v>
@@ -857,17 +857,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C19">
-        <v>1269</v>
+        <v>495</v>
       </c>
       <c r="D19">
         <v>2550</v>
       </c>
       <c r="E19">
-        <v>495</v>
+        <v>1269</v>
       </c>
       <c r="I19">
         <v>-774</v>
@@ -882,17 +882,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C20">
-        <v>1229</v>
+        <v>730</v>
       </c>
       <c r="D20">
         <v>2987</v>
       </c>
       <c r="E20">
-        <v>730</v>
+        <v>1229</v>
       </c>
       <c r="I20">
         <v>-499</v>
@@ -907,17 +907,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C21">
-        <v>1364</v>
+        <v>723</v>
       </c>
       <c r="D21">
         <v>3234</v>
       </c>
       <c r="E21">
-        <v>723</v>
+        <v>1364</v>
       </c>
       <c r="I21">
         <v>-641</v>
@@ -932,17 +932,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C22">
-        <v>1656</v>
+        <v>758</v>
       </c>
       <c r="D22">
         <v>3630</v>
       </c>
       <c r="E22">
-        <v>758</v>
+        <v>1656</v>
       </c>
       <c r="I22">
         <v>-898</v>
@@ -957,17 +957,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C23">
-        <v>2113</v>
+        <v>1123</v>
       </c>
       <c r="D23">
         <v>5151</v>
       </c>
       <c r="E23">
-        <v>1123</v>
+        <v>2113</v>
       </c>
       <c r="I23">
         <v>-990</v>
@@ -982,17 +982,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C24">
-        <v>2597</v>
+        <v>1295</v>
       </c>
       <c r="D24">
         <v>6323</v>
       </c>
       <c r="E24">
-        <v>1295</v>
+        <v>2597</v>
       </c>
       <c r="I24">
         <v>-1302</v>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C25">
-        <v>3355</v>
+        <v>1461</v>
       </c>
       <c r="D25">
         <v>7660</v>
       </c>
       <c r="E25">
-        <v>1461</v>
+        <v>3355</v>
       </c>
       <c r="I25">
         <v>-1894</v>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C26">
-        <v>3808</v>
+        <v>1696</v>
       </c>
       <c r="D26">
         <v>9274</v>
       </c>
       <c r="E26">
-        <v>1696</v>
+        <v>3808</v>
       </c>
       <c r="I26">
         <v>-2112</v>
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C27">
-        <v>4849</v>
+        <v>1947</v>
       </c>
       <c r="D27">
         <v>10832</v>
       </c>
       <c r="E27">
-        <v>1947</v>
+        <v>4849</v>
       </c>
       <c r="I27">
         <v>-2902</v>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C28">
-        <v>5282</v>
+        <v>2155</v>
       </c>
       <c r="D28">
         <v>11850</v>
       </c>
       <c r="E28">
-        <v>2155</v>
+        <v>5282</v>
       </c>
       <c r="I28">
         <v>-3127</v>
@@ -1107,17 +1107,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C29">
-        <v>6301</v>
+        <v>2366</v>
       </c>
       <c r="D29">
         <v>14372</v>
       </c>
       <c r="E29">
-        <v>2366</v>
+        <v>6301</v>
       </c>
       <c r="I29">
         <v>-3935</v>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C30">
-        <v>6248</v>
+        <v>2418</v>
       </c>
       <c r="D30">
         <v>15605</v>
       </c>
       <c r="E30">
-        <v>2418</v>
+        <v>6248</v>
       </c>
       <c r="I30">
         <v>-3830</v>
@@ -1157,17 +1157,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C31">
-        <v>6037</v>
+        <v>2339</v>
       </c>
       <c r="D31">
         <v>14870</v>
       </c>
       <c r="E31">
-        <v>2339</v>
+        <v>6037</v>
       </c>
       <c r="I31">
         <v>-3698</v>
@@ -1182,17 +1182,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C32">
-        <v>5212</v>
+        <v>2021</v>
       </c>
       <c r="D32">
         <v>13532</v>
       </c>
       <c r="E32">
-        <v>2021</v>
+        <v>5212</v>
       </c>
       <c r="I32">
         <v>-3191</v>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C33">
-        <v>6156</v>
+        <v>2344</v>
       </c>
       <c r="D33">
         <v>16144</v>
       </c>
       <c r="E33">
-        <v>2344</v>
+        <v>6156</v>
       </c>
       <c r="I33">
         <v>-3812</v>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C34">
-        <v>6386</v>
+        <v>2275</v>
       </c>
       <c r="D34">
         <v>15467</v>
       </c>
       <c r="E34">
-        <v>2275</v>
+        <v>6386</v>
       </c>
       <c r="I34">
         <v>-4111</v>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C35">
-        <v>6137</v>
+        <v>2206</v>
       </c>
       <c r="D35">
         <v>15239</v>
       </c>
       <c r="E35">
-        <v>2206</v>
+        <v>6137</v>
       </c>
       <c r="I35">
         <v>-3931</v>
